--- a/assets/constructions/examples/ctd_mib_hf.xlsx
+++ b/assets/constructions/examples/ctd_mib_hf.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,59 +594,79 @@
           <t>dbc2</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SKS08-50-22-4T</t>
+          <t>MT219-066A22R06FO12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SKS</t>
-        </is>
-      </c>
+          <t>СКИФ-М</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
         <v>22</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>40</v>
+      </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>16000</v>
+      </c>
       <c r="O2" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>WDMW080520ZTR/WDMT080520ZER/WDHW080520ZTR</t>
-        </is>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+          <t>FONT120412..R</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>19</v>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -663,106 +683,108 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>DER_WD0805H</t>
+          <t>SKIF_FO1204H</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>WD0805_H</t>
+          <t>SKIF_FO1204H</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
+          <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FHF-ENMX06-D40Z6S16</t>
+          <t>066A06815-05-02-027050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YG1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ENMX 0604</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>40</v>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>32.6</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ENMX0604</t>
+          <t xml:space="preserve">SOEW 160512 S /SOET 160520-MS </t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ISO_6462:FDAxx027</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>PALB_SO1605H</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>ISO_6462:FDAxx016</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>YG1_EN0604H</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
       </c>
       <c r="Z3" t="n">
         <v>4</v>
@@ -772,74 +794,86 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>YG1_EN0604H</t>
+          <t>PAL_SO1605_H</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
+          <t>2021/General catalogue</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>420.12</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>38623.19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R210-100Q32-14H</t>
+          <t>M1200HF080Z06HN09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CoroMillⓇ 210 face milling cutter</t>
+          <t>M1200</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
       <c r="H4" t="n">
         <v>50</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>50</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>13400</v>
+        <v>7300</v>
       </c>
       <c r="O4" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>CoroMill 210 -size 14 (R210-140512M/E-)</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>2.2</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -852,35 +886,45 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>COR_R210-1405H</t>
+          <t>WIDIA_XHN0905H</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>SAND_R210-1405_H</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+          <t>WID_XHN0905_H</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>WID_M1200D_137</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
+          <t>2017 / WIDIA основной каталог EN</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -974,58 +1018,62 @@
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AJX14-63-22-4T</t>
+          <t>066C50560-05-05-027053</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AJX</t>
-        </is>
-      </c>
+          <t>PALBIT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>53</v>
+      </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>JDMW140520</t>
-        </is>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
+          <t>WDET 120420-MS/WDMW 120420-T</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>0</v>
@@ -1034,39 +1082,53 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>DER_JD1405H</t>
+          <t>PALB_WD1204H</t>
         </is>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>JD1405_H</t>
+          <t>PAL_WD1204_H</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
+          <t>2021/General catalogue</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>427.23</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>39276.83</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
